--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\RiderProjects\architecture-sprint-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCA850D7-57B8-4221-AE76-8C4CBF67BC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368E5134-C83B-4B55-BA1E-135DE8CDFC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6510" yWindow="2805" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6855" yWindow="3150" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Код</t>
   </si>
@@ -167,6 +167,18 @@
   </si>
   <si>
     <t>Гарантирует соответствие внутренним требованиям безопасности.</t>
+  </si>
+  <si>
+    <t>Использование языка Java</t>
+  </si>
+  <si>
+    <t>Использование Java позволяет быстро интегрировать новые компоненты с уже существующими системами банка и минимизировать обучение для разработчиков</t>
+  </si>
+  <si>
+    <t>Использование очереди сообщений Kafka</t>
+  </si>
+  <si>
+    <t>Kafka поможет обрабатывать больше объемы данных в режиме реального времени, что важно для обеспечения быстрого отклика и масштабирования интернет-банка. Интеграция Kafka с существующими системами поможет избежать прямой работы в интернет-банка с API АБС, разгрузив основуную базу данных.</t>
   </si>
 </sst>
 </file>
@@ -307,14 +319,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -543,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="2" max="2" width="6.85546875" customWidth="1"/>
@@ -568,10 +580,10 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" spans="2:4" ht="30" customHeight="1">
       <c r="B5" s="2"/>
@@ -596,7 +608,7 @@
       <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -640,10 +652,10 @@
       <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="10"/>
+      <c r="D12" s="11"/>
     </row>
     <row r="13" spans="2:4" ht="30" customHeight="1">
       <c r="B13" s="2"/>
@@ -667,10 +679,10 @@
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="11"/>
     </row>
     <row r="16" spans="2:4" ht="30" customHeight="1">
       <c r="B16" s="2"/>
@@ -694,10 +706,10 @@
       <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="11"/>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="B19" s="2"/>
@@ -721,10 +733,10 @@
       <c r="B21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="10"/>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="B22" s="2"/>
@@ -748,10 +760,10 @@
       <c r="B24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="10"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" spans="1:4" ht="35.25" customHeight="1">
       <c r="A25" s="8"/>
@@ -763,13 +775,33 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="57.75" customHeight="1">
+    <row r="26" spans="1:4" ht="66" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="5"/>
       <c r="C26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="109.5" customHeight="1">
+      <c r="A27" s="8"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="57.75" customHeight="1">
+      <c r="A28" s="8"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>48</v>
       </c>
     </row>
